--- a/reports/william_arjona/perfil_estatistico_anual.xlsx
+++ b/reports/william_arjona/perfil_estatistico_anual.xlsx
@@ -42,11 +42,12 @@
     <sheet name="ONS_HORAS_UG_MENSAL" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="ONS_TEIFA_TEIP" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="ONS_DECOMPOSICAO_TAXAS" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="ONS_DIVERGENCIAS" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="CAD_FICHA" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="CAD_AUDITORIA" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="DICIONARIOS" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="FONTES" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="ONS_TAXAS_OPERATIVAS" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="ONS_DIVERGENCIAS" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="CAD_FICHA" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="CAD_AUDITORIA" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="DICIONARIOS" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="FONTES" sheetId="41" state="visible" r:id="rId41"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +484,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Série de referência: Geração por usina (id ONS MSUTWI), de 10/07/2021 00h a 18/10/2026 23h: 46.243 horas com registro de 46.248 no período (99,99%). 5 horas ausentes, listadas na planilha, sem preenchimento. O período tem 3 trechos, com mudança de modalidade, de composição do conjunto ou de código.</t>
+          <t>Série de referência: Geração por usina (id ONS MSUTWI), de 10/07/2021 00h a 24/10/2026 23h: 46.387 horas com registro de 46.392 no período (99,99%). 5 horas ausentes, listadas na planilha, sem preenchimento. O período tem 3 trechos, com mudança de modalidade, de composição do conjunto ou de código.</t>
         </is>
       </c>
     </row>
@@ -495,7 +496,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geração média de 6,6 MWmed nas 46.243 horas com valor (306.749 MWh); geração até 1 MW em 92,8% das horas; entre os anos completos, maior média em 2022 (0,6 MWmed) e menor em 2023 (0,0 MWmed).</t>
+          <t>Geração média de 6,6 MWmed nas 46.387 horas com valor (307.484 MWh); geração até 1 MW em 92,8% das horas; entre os anos completos, maior média em 2022 (0,6 MWmed) e menor em 2023 (0,0 MWmed).</t>
         </is>
       </c>
     </row>
@@ -507,7 +508,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Disponibilidade operacional média de 38,4 MW (21,7% da potência instalada) e sincronizada de 7,0 MW, nas 46.243 horas com o dado; indisponibilidade total em 32.140 horas (22 eventos); geração acima da disponibilidade declarada em 1.322 horas.</t>
+          <t>Disponibilidade operacional média de 38,8 MW (21,9% da potência instalada) e sincronizada de 7,0 MW, nas 46.387 horas com o dado; indisponibilidade total em 32.140 horas (22 eventos); geração acima da disponibilidade declarada em 1.320 horas.</t>
         </is>
       </c>
     </row>
@@ -519,7 +520,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nas 5.760 horas com programação e geração verificada, geração verificada média de 1,6 MW e programada de 2,0 MW (desvio médio absoluto de 0,7 MW; correlação de 0,93); 3 horas com geração até 1 MW e programação acima de 5 MW.</t>
+          <t>Nas 5.880 horas com programação e geração verificada, geração verificada média de 1,7 MW e programada de 2,1 MW (desvio médio absoluto de 0,8 MW; correlação de 0,93); 2 horas com geração até 1 MW e programação acima de 5 MW.</t>
         </is>
       </c>
     </row>
@@ -531,7 +532,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geração verificada do despacho de 304.357 MWh de 10/07/2021 a 18/10/2026 (unidades de planejamento 334 e 434); geração programada em 3.264 horas. Maior motivo verificado: garantia energética, com 69,6% da geração verificada.</t>
+          <t>Geração verificada do despacho de 305.063 MWh de 10/07/2021 a 19/10/2026 (unidades de planejamento 334 e 434); geração programada em 3.271 horas. Maior motivo verificado: garantia energética, com 69,5% da geração verificada.</t>
         </is>
       </c>
     </row>
@@ -543,7 +544,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nas 3.264 horas com geração programada, a verificada ficou mais de 5 MW abaixo da programada em 2.821 horas (112.233 MWh) e acima em 86 horas (1.828 MWh); sem programação, geração acima de 5 MW em 114 horas.</t>
+          <t>Nas 3.271 horas com geração programada, a verificada ficou mais de 5 MW abaixo da programada em 2.826 horas (112.445 MWh) e acima em 88 horas (1.875 MWh); sem programação, geração acima de 5 MW em 114 horas.</t>
         </is>
       </c>
     </row>
@@ -555,7 +556,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disponível, sem programação e sem geração em 10.856 das 46.243 horas com a disponibilidade e o despacho (23,5%), com a potência disponível média de 134,0 MW.</t>
+          <t>Disponível, sem programação e sem geração em 10.873 das 46.267 horas com a disponibilidade e o despacho (23,5%), com a potência disponível média de 134,4 MW.</t>
         </is>
       </c>
     </row>
@@ -579,7 +580,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.322 horas sinalizadas (2,86% das horas; R7, geração acima da disponibilidade declarada: 1.322 h), mantidas na base e nos totais.</t>
+          <t>1.320 horas sinalizadas (2,85% das horas; R7, geração acima da disponibilidade declarada: 1.320 h), mantidas na base e nos totais.</t>
         </is>
       </c>
     </row>
@@ -3495,31 +3496,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>432</v>
+        <v>576</v>
       </c>
       <c r="C65" t="n">
-        <v>144.1531560786366</v>
+        <v>152.7156835815469</v>
       </c>
       <c r="D65" t="n">
-        <v>0.547792960425926</v>
+        <v>1.635416105416667</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9212395833333333</v>
+        <v>1.967263020833333</v>
       </c>
       <c r="F65" t="n">
-        <v>143.6053631182106</v>
+        <v>151.0802674761302</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>425</v>
+        <v>561</v>
       </c>
       <c r="I65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3819,37 +3820,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6979</v>
+        <v>7123</v>
       </c>
       <c r="C7" t="n">
-        <v>141.4521407257427</v>
+        <v>142.1991521047253</v>
       </c>
       <c r="D7" t="n">
-        <v>4.130426477547069</v>
+        <v>4.145949670731012</v>
       </c>
       <c r="E7" t="n">
-        <v>1.433203754119501</v>
+        <v>1.507440263933736</v>
       </c>
       <c r="F7" t="n">
-        <v>137.3217142481956</v>
+        <v>138.0532024339942</v>
       </c>
       <c r="G7" t="n">
         <v>190</v>
       </c>
       <c r="H7" t="n">
-        <v>6657</v>
+        <v>6793</v>
       </c>
       <c r="I7" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="J7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>79.86412335742827</v>
+        <v>80.28588727428649</v>
       </c>
     </row>
   </sheetData>
@@ -4451,22 +4452,22 @@
         <v>46296</v>
       </c>
       <c r="B10" t="n">
-        <v>432</v>
+        <v>552</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9212395833333333</v>
+        <v>2.025172101449275</v>
       </c>
       <c r="D10" t="n">
-        <v>2.465277777777778</v>
+        <v>3.504528985507247</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.544038194444444</v>
+        <v>-1.479356884057971</v>
       </c>
       <c r="F10" t="n">
-        <v>1.622457175925926</v>
+        <v>1.704596014492753</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -4480,7 +4481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -4537,20 +4538,6 @@
       </c>
       <c r="D3" t="n">
         <v>90</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="n">
-        <v>46310.66666666666</v>
-      </c>
-      <c r="B4" s="1" t="n">
-        <v>46310.66666666666</v>
-      </c>
-      <c r="C4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" t="n">
-        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -6127,10 +6114,10 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12876.5</v>
+        <v>13746</v>
       </c>
       <c r="E57" t="n">
-        <v>10002.326</v>
+        <v>10707.578</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
@@ -6158,10 +6145,10 @@
         <v>4185.651</v>
       </c>
       <c r="F58" t="n">
-        <v>45.55197452723954</v>
+        <v>42.67059508220573</v>
       </c>
       <c r="G58" t="n">
-        <v>41.8467764398001</v>
+        <v>39.09054876835826</v>
       </c>
     </row>
     <row r="59">
@@ -6184,13 +6171,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>985.0549999999998</v>
+        <v>985.0549999999999</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9.848259294888006</v>
+        <v>9.199606110737648</v>
       </c>
     </row>
     <row r="60">
@@ -6210,16 +6197,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>2967.5</v>
+        <v>3587</v>
       </c>
       <c r="E60" t="n">
-        <v>1746.256</v>
+        <v>2225.974</v>
       </c>
       <c r="F60" t="n">
-        <v>23.04585873490467</v>
+        <v>26.09486396042485</v>
       </c>
       <c r="G60" t="n">
-        <v>17.45849915309699</v>
+        <v>20.78877221347349</v>
       </c>
     </row>
     <row r="61">
@@ -6268,16 +6255,16 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>4043.5</v>
+        <v>4293.5</v>
       </c>
       <c r="E62" t="n">
-        <v>3085.373000000001</v>
+        <v>3310.907</v>
       </c>
       <c r="F62" t="n">
-        <v>31.40216673785579</v>
+        <v>31.23454095736942</v>
       </c>
       <c r="G62" t="n">
-        <v>30.84655509128577</v>
+        <v>30.92115696005203</v>
       </c>
     </row>
     <row r="63">
@@ -6306,7 +6293,7 @@
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>9.728897058544183</v>
+        <v>9.088105638828875</v>
       </c>
     </row>
     <row r="64">
@@ -6335,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1193622363438264</v>
+        <v>0.1115004719087734</v>
       </c>
     </row>
     <row r="65">
@@ -6361,10 +6348,10 @@
         <v>4185.651</v>
       </c>
       <c r="F65" t="n">
-        <v>45.55197452723954</v>
+        <v>42.67059508220573</v>
       </c>
       <c r="G65" t="n">
-        <v>41.8467764398001</v>
+        <v>39.09054876835826</v>
       </c>
     </row>
     <row r="66">
@@ -6388,7 +6375,7 @@
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>67.64828951966761</v>
+        <v>63.36921286192347</v>
       </c>
       <c r="G66" t="inlineStr"/>
     </row>
@@ -6415,10 +6402,10 @@
         <v>2247.504</v>
       </c>
       <c r="F67" t="n">
-        <v>22.04015066205879</v>
+        <v>20.64600611086862</v>
       </c>
       <c r="G67" t="n">
-        <v>22.46981352137493</v>
+        <v>20.98984476227957</v>
       </c>
     </row>
   </sheetData>
@@ -24205,10 +24192,10 @@
         </is>
       </c>
       <c r="D695" t="n">
-        <v>1065</v>
+        <v>1934.5</v>
       </c>
       <c r="E695" t="n">
-        <v>397.976</v>
+        <v>1103.228</v>
       </c>
       <c r="F695" t="inlineStr"/>
       <c r="G695" t="inlineStr"/>
@@ -24268,7 +24255,7 @@
         <v>0</v>
       </c>
       <c r="G697" t="n">
-        <v>4.256538082698454</v>
+        <v>1.53549402299434</v>
       </c>
     </row>
     <row r="698">
@@ -24288,16 +24275,16 @@
         </is>
       </c>
       <c r="D698" t="n">
-        <v>885</v>
+        <v>1504.5</v>
       </c>
       <c r="E698" t="n">
-        <v>314.975</v>
+        <v>794.693</v>
       </c>
       <c r="F698" t="n">
-        <v>83.09859154929578</v>
+        <v>77.77203411734298</v>
       </c>
       <c r="G698" t="n">
-        <v>79.14421975194485</v>
+        <v>72.03343279902251</v>
       </c>
     </row>
     <row r="699">
@@ -24346,16 +24333,16 @@
         </is>
       </c>
       <c r="D700" t="n">
-        <v>180</v>
+        <v>430</v>
       </c>
       <c r="E700" t="n">
-        <v>66.06099999999999</v>
+        <v>291.595</v>
       </c>
       <c r="F700" t="n">
-        <v>16.90140845070422</v>
+        <v>22.22796588265702</v>
       </c>
       <c r="G700" t="n">
-        <v>16.5992421653567</v>
+        <v>26.43107317798315</v>
       </c>
     </row>
     <row r="701">
@@ -24384,7 +24371,7 @@
         <v>0</v>
       </c>
       <c r="G701" t="n">
-        <v>4.256538082698454</v>
+        <v>1.53549402299434</v>
       </c>
     </row>
     <row r="702">
@@ -24510,7 +24497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -24563,7 +24550,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Geração acima da disponibilidade declarada em 1.322 h, segundo a regra R7</t>
+          <t>Geração acima da disponibilidade declarada em 1.320 h, segundo a regra R7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24588,7 +24575,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.821 h (112.233 MWh)</t>
+          <t>Geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.826 h (112.445 MWh)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24613,7 +24600,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Critério e horário da declaração de disponibilidade ao ONS, dado que a geração superou a disponibilidade declarada em 1.322 h</t>
+          <t>Critério e horário da declaração de disponibilidade ao ONS, dado que a geração superou a disponibilidade declarada em 1.320 h</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -24663,7 +24650,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Motivo da geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.821 h (112.233 MWh)</t>
+          <t>Motivo da geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.826 h (112.445 MWh)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -24700,23 +24687,48 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>A confirmar com o agente</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>C20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Motivo da diferença entre as taxas operativas e as oficiais do ONS em set/2026: TEIFa operativa de 12,89% e oficial de 30,07% (diferença de −17,18 p.p.); TEIP operativa de 58,98% e oficial de 70,30% (diferença de −11,32 p.p.)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>4. Indicadores oficiais do ONS por unidade geradora</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>A verificar em campo</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="B9" t="n">
         <v>1</v>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>C10</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>Plano e registros de manutenção preventiva e corretiva das unidades geradoras, em especial de 2022, 2023, 2024 e 2025</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>3. Disponibilidade e geração por ano; 4. Indicadores oficiais do ONS por unidade geradora</t>
         </is>
@@ -25861,19 +25873,19 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D7" t="n">
-        <v>3777.022</v>
+        <v>3988.218</v>
       </c>
       <c r="E7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F7" t="n">
-        <v>265.358</v>
+        <v>312.306</v>
       </c>
       <c r="G7" t="n">
         <v>19</v>
@@ -26616,10 +26628,10 @@
         <v>46296</v>
       </c>
       <c r="B65" t="n">
-        <v>683.963</v>
+        <v>895.159</v>
       </c>
       <c r="C65" t="n">
-        <v>16.939</v>
+        <v>63.887</v>
       </c>
     </row>
   </sheetData>
@@ -26989,13 +27001,13 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>6979</v>
+        <v>7003</v>
       </c>
       <c r="C7" t="n">
-        <v>6654</v>
+        <v>6671</v>
       </c>
       <c r="D7" t="n">
-        <v>145.6797888307579</v>
+        <v>146.2460621641228</v>
       </c>
     </row>
   </sheetData>
@@ -44184,10 +44196,10 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>0</v>
+        <v>705.252</v>
       </c>
       <c r="I541" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="542">
@@ -44220,7 +44232,7 @@
         <v>0</v>
       </c>
       <c r="I542" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -44312,7 +44324,7 @@
         <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>83884.79150000001</v>
+        <v>84590.0435</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -46190,22 +46202,22 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1065</v>
+        <v>1934.5</v>
       </c>
       <c r="C65" t="n">
-        <v>1065</v>
+        <v>1934.5</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -48048,25 +48060,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>397.976</v>
+        <v>1103.228</v>
       </c>
       <c r="C65" t="n">
-        <v>397.9755</v>
+        <v>1109.2865</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0004999999999881766</v>
+        <v>-6.058499999999867</v>
       </c>
       <c r="E65" t="n">
-        <v>432</v>
+        <v>456</v>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -48080,7 +48092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -48285,6 +48297,23 @@
       </c>
       <c r="E11" t="n">
         <v>0.2000000000000028</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>46310.66666666666</v>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>46310.95833333334</v>
+      </c>
+      <c r="C12" t="n">
+        <v>8</v>
+      </c>
+      <c r="D12" t="n">
+        <v>12.8486875</v>
+      </c>
+      <c r="E12" t="n">
+        <v>32.777</v>
       </c>
     </row>
   </sheetData>
@@ -48601,32 +48630,32 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>6979</v>
+        <v>7123</v>
       </c>
       <c r="E7" t="n">
-        <v>6979</v>
+        <v>7123</v>
       </c>
       <c r="F7" t="n">
-        <v>1.433203754119502</v>
+        <v>1.507440263933736</v>
       </c>
       <c r="G7" t="n">
-        <v>10002.329</v>
+        <v>10737.497</v>
       </c>
       <c r="H7" t="n">
         <v>154.712</v>
       </c>
       <c r="I7" t="n">
-        <v>6847</v>
+        <v>6983</v>
       </c>
       <c r="J7" t="n">
-        <v>98.10861154893252</v>
+        <v>98.0345360101081</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>141.4521407257427</v>
+        <v>142.1991521047252</v>
       </c>
       <c r="M7" t="n">
-        <v>79.86412335742827</v>
+        <v>80.28588727428647</v>
       </c>
     </row>
   </sheetData>
@@ -48802,7 +48831,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>79.86412335742827</v>
+        <v>80.28588727428647</v>
       </c>
       <c r="D7" t="n">
         <v>99.14499062125448</v>
@@ -67302,6 +67331,1469 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G62"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>mes</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>teifa_pct</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>teifa_oper_pct</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>teip_pct</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>teip_oper_pct</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dif_teifa_pp</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dif_teip_pp</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B2" t="n">
+        <v>4.017243000000001</v>
+      </c>
+      <c r="C2" t="n">
+        <v>4.017243000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.82419</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1.82419</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B3" t="n">
+        <v>4.627661000000001</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4.627969</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.808257</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.808257</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0003079999999995309</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B4" t="n">
+        <v>4.948309</v>
+      </c>
+      <c r="C4" t="n">
+        <v>4.948638000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.78286</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1.78286</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0003290000000006899</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B5" t="n">
+        <v>5.254051</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5.254401000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0003500000000009607</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B6" t="n">
+        <v>5.816443</v>
+      </c>
+      <c r="C6" t="n">
+        <v>5.254401000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.785835</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.5620419999999999</v>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.917443</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B7" t="n">
+        <v>6.204384</v>
+      </c>
+      <c r="C7" t="n">
+        <v>5.254401000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>3.963081</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.9499829999999996</v>
+      </c>
+      <c r="G7" t="n">
+        <v>-2.094689</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6.645138</v>
+      </c>
+      <c r="C8" t="n">
+        <v>5.254401000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5.266459999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.390737</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-3.398067999999999</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7.083377</v>
+      </c>
+      <c r="C9" t="n">
+        <v>5.254401000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>6.527795</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-1.828976</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-4.659403</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B10" t="n">
+        <v>7.548825000000001</v>
+      </c>
+      <c r="C10" t="n">
+        <v>5.254401000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>7.831173</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-2.294424</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-5.962781</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B11" t="n">
+        <v>8.011967</v>
+      </c>
+      <c r="C11" t="n">
+        <v>5.254401000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>9.092508</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.868392</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-2.757566</v>
+      </c>
+      <c r="G11" t="n">
+        <v>-7.224116</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B12" t="n">
+        <v>8.504245000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>5.163932</v>
+      </c>
+      <c r="D12" t="n">
+        <v>10.395887</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.807712</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-3.340313000000001</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-8.588175</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B13" t="n">
+        <v>8.223796</v>
+      </c>
+      <c r="C13" t="n">
+        <v>5.144362</v>
+      </c>
+      <c r="D13" t="n">
+        <v>12.456713</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2.250748</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-3.079434</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-10.205965</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B14" t="n">
+        <v>8.332245</v>
+      </c>
+      <c r="C14" t="n">
+        <v>5.189098</v>
+      </c>
+      <c r="D14" t="n">
+        <v>14.084558</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.876796</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-3.143147</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-10.207762</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B15" t="n">
+        <v>8.448713</v>
+      </c>
+      <c r="C15" t="n">
+        <v>5.133143</v>
+      </c>
+      <c r="D15" t="n">
+        <v>15.766665</v>
+      </c>
+      <c r="E15" t="n">
+        <v>5.446957</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-3.31557</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B16" t="n">
+        <v>8.565939</v>
+      </c>
+      <c r="C16" t="n">
+        <v>5.179273</v>
+      </c>
+      <c r="D16" t="n">
+        <v>17.39451</v>
+      </c>
+      <c r="E16" t="n">
+        <v>7.074801999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-3.386666</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B17" t="n">
+        <v>8.692029</v>
+      </c>
+      <c r="C17" t="n">
+        <v>5.228671</v>
+      </c>
+      <c r="D17" t="n">
+        <v>19.076617</v>
+      </c>
+      <c r="E17" t="n">
+        <v>8.756909</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-3.463357999999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8.823467000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>5.279921</v>
+      </c>
+      <c r="D18" t="n">
+        <v>20.758685</v>
+      </c>
+      <c r="E18" t="n">
+        <v>10.438977</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-3.543546000000001</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B19" t="n">
+        <v>8.947078999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5.327897</v>
+      </c>
+      <c r="D19" t="n">
+        <v>22.278007</v>
+      </c>
+      <c r="E19" t="n">
+        <v>11.958299</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-3.619181999999999</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B20" t="n">
+        <v>9.089696999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>5.382983</v>
+      </c>
+      <c r="D20" t="n">
+        <v>23.960114</v>
+      </c>
+      <c r="E20" t="n">
+        <v>13.640406</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-3.706713999999999</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B21" t="n">
+        <v>9.233853999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5.438375</v>
+      </c>
+      <c r="D21" t="n">
+        <v>25.587959</v>
+      </c>
+      <c r="E21" t="n">
+        <v>15.268251</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-3.795478999999999</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B22" t="n">
+        <v>9.389595</v>
+      </c>
+      <c r="C22" t="n">
+        <v>5.497894</v>
+      </c>
+      <c r="D22" t="n">
+        <v>27.270065</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.950357</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.891701</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B23" t="n">
+        <v>9.547329</v>
+      </c>
+      <c r="C23" t="n">
+        <v>5.557835</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28.897911</v>
+      </c>
+      <c r="E23" t="n">
+        <v>18.578202</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-3.989494</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-10.319709</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B24" t="n">
+        <v>9.718092</v>
+      </c>
+      <c r="C24" t="n">
+        <v>5.622345</v>
+      </c>
+      <c r="D24" t="n">
+        <v>30.580017</v>
+      </c>
+      <c r="E24" t="n">
+        <v>20.260309</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-4.095747</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-10.31970799999999</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B25" t="n">
+        <v>9.897335999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>5.689636</v>
+      </c>
+      <c r="D25" t="n">
+        <v>32.262124</v>
+      </c>
+      <c r="E25" t="n">
+        <v>21.942416</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-4.207699999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B26" t="n">
+        <v>10.079482</v>
+      </c>
+      <c r="C26" t="n">
+        <v>5.757575999999999</v>
+      </c>
+      <c r="D26" t="n">
+        <v>33.889969</v>
+      </c>
+      <c r="E26" t="n">
+        <v>23.570261</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-4.321905999999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B27" t="n">
+        <v>10.27737</v>
+      </c>
+      <c r="C27" t="n">
+        <v>5.830891</v>
+      </c>
+      <c r="D27" t="n">
+        <v>35.572076</v>
+      </c>
+      <c r="E27" t="n">
+        <v>25.252367</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-4.446478999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-10.319709</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B28" t="n">
+        <v>10.478968</v>
+      </c>
+      <c r="C28" t="n">
+        <v>5.905052</v>
+      </c>
+      <c r="D28" t="n">
+        <v>37.199921</v>
+      </c>
+      <c r="E28" t="n">
+        <v>26.880213</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-4.573916</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-10.31970800000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B29" t="n">
+        <v>10.955724</v>
+      </c>
+      <c r="C29" t="n">
+        <v>6.216974</v>
+      </c>
+      <c r="D29" t="n">
+        <v>38.705521</v>
+      </c>
+      <c r="E29" t="n">
+        <v>28.385813</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-4.73875</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B30" t="n">
+        <v>12.685393</v>
+      </c>
+      <c r="C30" t="n">
+        <v>7.650839</v>
+      </c>
+      <c r="D30" t="n">
+        <v>39.369628</v>
+      </c>
+      <c r="E30" t="n">
+        <v>29.04992</v>
+      </c>
+      <c r="F30" t="n">
+        <v>-5.034554000000002</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B31" t="n">
+        <v>14.327434</v>
+      </c>
+      <c r="C31" t="n">
+        <v>9.011689000000001</v>
+      </c>
+      <c r="D31" t="n">
+        <v>39.969798</v>
+      </c>
+      <c r="E31" t="n">
+        <v>29.655789</v>
+      </c>
+      <c r="F31" t="n">
+        <v>-5.315745</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B32" t="n">
+        <v>14.925887</v>
+      </c>
+      <c r="C32" t="n">
+        <v>9.404342999999999</v>
+      </c>
+      <c r="D32" t="n">
+        <v>41.474246</v>
+      </c>
+      <c r="E32" t="n">
+        <v>31.160237</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-5.521544</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B33" t="n">
+        <v>15.281189</v>
+      </c>
+      <c r="C33" t="n">
+        <v>9.571485000000001</v>
+      </c>
+      <c r="D33" t="n">
+        <v>43.101192</v>
+      </c>
+      <c r="E33" t="n">
+        <v>32.787183</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-5.709704</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B34" t="n">
+        <v>15.67033</v>
+      </c>
+      <c r="C34" t="n">
+        <v>9.752917999999999</v>
+      </c>
+      <c r="D34" t="n">
+        <v>44.78237</v>
+      </c>
+      <c r="E34" t="n">
+        <v>34.46836099999999</v>
+      </c>
+      <c r="F34" t="n">
+        <v>-5.917412000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-10.31400900000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B35" t="n">
+        <v>16.070165</v>
+      </c>
+      <c r="C35" t="n">
+        <v>9.937588</v>
+      </c>
+      <c r="D35" t="n">
+        <v>46.409316</v>
+      </c>
+      <c r="E35" t="n">
+        <v>36.095307</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-6.132577</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-10.31400900000001</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B36" t="n">
+        <v>16.509657</v>
+      </c>
+      <c r="C36" t="n">
+        <v>10.138561</v>
+      </c>
+      <c r="D36" t="n">
+        <v>48.090494</v>
+      </c>
+      <c r="E36" t="n">
+        <v>37.776485</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-6.371096000000001</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B37" t="n">
+        <v>16.978571</v>
+      </c>
+      <c r="C37" t="n">
+        <v>10.350696</v>
+      </c>
+      <c r="D37" t="n">
+        <v>49.771671</v>
+      </c>
+      <c r="E37" t="n">
+        <v>39.457662</v>
+      </c>
+      <c r="F37" t="n">
+        <v>-6.627875000000003</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45536</v>
+      </c>
+      <c r="B38" t="n">
+        <v>17.463245</v>
+      </c>
+      <c r="C38" t="n">
+        <v>10.567517</v>
+      </c>
+      <c r="D38" t="n">
+        <v>51.398618</v>
+      </c>
+      <c r="E38" t="n">
+        <v>41.084609</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-6.895728</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B39" t="n">
+        <v>17.999387</v>
+      </c>
+      <c r="C39" t="n">
+        <v>10.804516</v>
+      </c>
+      <c r="D39" t="n">
+        <v>53.079795</v>
+      </c>
+      <c r="E39" t="n">
+        <v>42.765786</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-7.194870999999999</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B40" t="n">
+        <v>18.556129</v>
+      </c>
+      <c r="C40" t="n">
+        <v>11.047517</v>
+      </c>
+      <c r="D40" t="n">
+        <v>54.706741</v>
+      </c>
+      <c r="E40" t="n">
+        <v>44.392732</v>
+      </c>
+      <c r="F40" t="n">
+        <v>-7.508611999999999</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B41" t="n">
+        <v>19.175068</v>
+      </c>
+      <c r="C41" t="n">
+        <v>11.314023</v>
+      </c>
+      <c r="D41" t="n">
+        <v>56.387919</v>
+      </c>
+      <c r="E41" t="n">
+        <v>46.07391</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-7.861045000000001</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B42" t="n">
+        <v>20.140547</v>
+      </c>
+      <c r="C42" t="n">
+        <v>11.860717</v>
+      </c>
+      <c r="D42" t="n">
+        <v>57.913202</v>
+      </c>
+      <c r="E42" t="n">
+        <v>47.599193</v>
+      </c>
+      <c r="F42" t="n">
+        <v>-8.279830000000002</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-10.314009</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B43" t="n">
+        <v>20.825335</v>
+      </c>
+      <c r="C43" t="n">
+        <v>12.150392</v>
+      </c>
+      <c r="D43" t="n">
+        <v>59.46353</v>
+      </c>
+      <c r="E43" t="n">
+        <v>49.143822</v>
+      </c>
+      <c r="F43" t="n">
+        <v>-8.674942999999999</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B44" t="n">
+        <v>21.618687</v>
+      </c>
+      <c r="C44" t="n">
+        <v>12.480548</v>
+      </c>
+      <c r="D44" t="n">
+        <v>61.14563699999999</v>
+      </c>
+      <c r="E44" t="n">
+        <v>50.825928</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-9.138139000000002</v>
+      </c>
+      <c r="G44" t="n">
+        <v>-10.319709</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B45" t="n">
+        <v>22.454711</v>
+      </c>
+      <c r="C45" t="n">
+        <v>12.8223</v>
+      </c>
+      <c r="D45" t="n">
+        <v>62.773482</v>
+      </c>
+      <c r="E45" t="n">
+        <v>52.453774</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-9.632410999999999</v>
+      </c>
+      <c r="G45" t="n">
+        <v>-10.31970800000001</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B46" t="n">
+        <v>23.399049</v>
+      </c>
+      <c r="C46" t="n">
+        <v>13.200934</v>
+      </c>
+      <c r="D46" t="n">
+        <v>64.45558799999999</v>
+      </c>
+      <c r="E46" t="n">
+        <v>54.13588</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-10.198115</v>
+      </c>
+      <c r="G46" t="n">
+        <v>-10.31970799999999</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B47" t="n">
+        <v>24.725014</v>
+      </c>
+      <c r="C47" t="n">
+        <v>13.878065</v>
+      </c>
+      <c r="D47" t="n">
+        <v>65.937943</v>
+      </c>
+      <c r="E47" t="n">
+        <v>55.61823500000001</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-10.846949</v>
+      </c>
+      <c r="G47" t="n">
+        <v>-10.319708</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B48" t="n">
+        <v>25.879582</v>
+      </c>
+      <c r="C48" t="n">
+        <v>14.32636</v>
+      </c>
+      <c r="D48" t="n">
+        <v>67.62004999999999</v>
+      </c>
+      <c r="E48" t="n">
+        <v>57.300342</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-11.553222</v>
+      </c>
+      <c r="G48" t="n">
+        <v>-10.31970799999999</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B49" t="n">
+        <v>27.147225</v>
+      </c>
+      <c r="C49" t="n">
+        <v>14.817451</v>
+      </c>
+      <c r="D49" t="n">
+        <v>69.18891600000001</v>
+      </c>
+      <c r="E49" t="n">
+        <v>58.849169</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-12.329774</v>
+      </c>
+      <c r="G49" t="n">
+        <v>-10.339747</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B50" t="n">
+        <v>28.179661</v>
+      </c>
+      <c r="C50" t="n">
+        <v>15.287361</v>
+      </c>
+      <c r="D50" t="n">
+        <v>70.06487</v>
+      </c>
+      <c r="E50" t="n">
+        <v>59.693323</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-12.8923</v>
+      </c>
+      <c r="G50" t="n">
+        <v>-10.371547</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B51" t="n">
+        <v>28.827571</v>
+      </c>
+      <c r="C51" t="n">
+        <v>15.670768</v>
+      </c>
+      <c r="D51" t="n">
+        <v>70.27015399999999</v>
+      </c>
+      <c r="E51" t="n">
+        <v>59.865541</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-13.156803</v>
+      </c>
+      <c r="G51" t="n">
+        <v>-10.40461299999999</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45962</v>
+      </c>
+      <c r="B52" t="n">
+        <v>29.46015</v>
+      </c>
+      <c r="C52" t="n">
+        <v>16.046353</v>
+      </c>
+      <c r="D52" t="n">
+        <v>70.457452</v>
+      </c>
+      <c r="E52" t="n">
+        <v>60.02063800000001</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-13.413797</v>
+      </c>
+      <c r="G52" t="n">
+        <v>-10.436814</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B53" t="n">
+        <v>30.471541</v>
+      </c>
+      <c r="C53" t="n">
+        <v>16.692625</v>
+      </c>
+      <c r="D53" t="n">
+        <v>70.652216</v>
+      </c>
+      <c r="E53" t="n">
+        <v>60.181918</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-13.778916</v>
+      </c>
+      <c r="G53" t="n">
+        <v>-10.47029799999999</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B54" t="n">
+        <v>31.477582</v>
+      </c>
+      <c r="C54" t="n">
+        <v>17.154343</v>
+      </c>
+      <c r="D54" t="n">
+        <v>71.038611</v>
+      </c>
+      <c r="E54" t="n">
+        <v>60.344235</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-14.323239</v>
+      </c>
+      <c r="G54" t="n">
+        <v>-10.694376</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B55" t="n">
+        <v>31.429651</v>
+      </c>
+      <c r="C55" t="n">
+        <v>16.613884</v>
+      </c>
+      <c r="D55" t="n">
+        <v>70.95624600000001</v>
+      </c>
+      <c r="E55" t="n">
+        <v>59.558776</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-14.81576699999999</v>
+      </c>
+      <c r="G55" t="n">
+        <v>-11.39747000000001</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B56" t="n">
+        <v>32.016563</v>
+      </c>
+      <c r="C56" t="n">
+        <v>16.509331</v>
+      </c>
+      <c r="D56" t="n">
+        <v>70.925271</v>
+      </c>
+      <c r="E56" t="n">
+        <v>59.527801</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-15.507232</v>
+      </c>
+      <c r="G56" t="n">
+        <v>-11.39746999999999</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B57" t="n">
+        <v>32.461835</v>
+      </c>
+      <c r="C57" t="n">
+        <v>16.396152</v>
+      </c>
+      <c r="D57" t="n">
+        <v>70.895295</v>
+      </c>
+      <c r="E57" t="n">
+        <v>59.49782500000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-16.065683</v>
+      </c>
+      <c r="G57" t="n">
+        <v>-11.39747</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B58" t="n">
+        <v>32.977835</v>
+      </c>
+      <c r="C58" t="n">
+        <v>16.279713</v>
+      </c>
+      <c r="D58" t="n">
+        <v>70.877205</v>
+      </c>
+      <c r="E58" t="n">
+        <v>59.467689</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-16.698122</v>
+      </c>
+      <c r="G58" t="n">
+        <v>-11.409516</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B59" t="n">
+        <v>33.445287</v>
+      </c>
+      <c r="C59" t="n">
+        <v>16.170263</v>
+      </c>
+      <c r="D59" t="n">
+        <v>70.85430599999999</v>
+      </c>
+      <c r="E59" t="n">
+        <v>59.44362</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-17.275024</v>
+      </c>
+      <c r="G59" t="n">
+        <v>-11.410686</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B60" t="n">
+        <v>32.473462</v>
+      </c>
+      <c r="C60" t="n">
+        <v>15.247338</v>
+      </c>
+      <c r="D60" t="n">
+        <v>70.463188</v>
+      </c>
+      <c r="E60" t="n">
+        <v>59.113839</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-17.226124</v>
+      </c>
+      <c r="G60" t="n">
+        <v>-11.349349</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B61" t="n">
+        <v>31.589302</v>
+      </c>
+      <c r="C61" t="n">
+        <v>14.400043</v>
+      </c>
+      <c r="D61" t="n">
+        <v>70.357012</v>
+      </c>
+      <c r="E61" t="n">
+        <v>59.041424</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-17.189259</v>
+      </c>
+      <c r="G61" t="n">
+        <v>-11.315588</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B62" t="n">
+        <v>30.071384</v>
+      </c>
+      <c r="C62" t="n">
+        <v>12.88669</v>
+      </c>
+      <c r="D62" t="n">
+        <v>70.29789</v>
+      </c>
+      <c r="E62" t="n">
+        <v>58.982302</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-17.184694</v>
+      </c>
+      <c r="G62" t="n">
+        <v>-11.315588</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -69200,7 +70692,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69345,7 +70837,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-20 11:58:03</t>
+          <t>2026-10-26 12:23:31</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -69369,7 +70861,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -69448,7 +70940,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6024</v>
+        <v>6034</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -69468,1364 +70960,6 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="25" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>conjunto</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>pasta</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>formato</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>arquivo</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>url</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>resultado_ultima_obtencao</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>obtido_em_utc</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>sha256</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>tamanho_bytes</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>versoes_anteriores</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>ultima_versao_anterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ind_disponibilidade_fgeracao_uge_mensal</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_mensal/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.pdf</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_me/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.pdf</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:09:55</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>9a7e03afa6c275128c94534ddb28d8608e6c79dd7915f5ca213f21cda6ea7a09</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>306461</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ind_disponibilidade_fgeracao_uge_mensal</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_mensal/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.json</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_me/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.json</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:09:55</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>8e4e092e95f037007a5d78adae5562487f63752db6bc4cf21f03ba0b2e98cac1</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>3367</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ind_disponibilidade_fgeracao_uge_anual</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_anual/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.pdf</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_an/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.pdf</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:09:59</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>344bf26d186b570cf2715f4389cc0928d184d58ff02fa7b72e299a1716b4bcdb</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>308635</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>ind_disponibilidade_fgeracao_uge_anual</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_anual/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.json</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_an/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.json</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:09:59</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>4c876daff676113179e80378f9e473e124d50a34e216d1e4ac5b33102612b431</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>3355</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>taxa_teif_teip_parametro</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>indicadores_ons/taxa_teif_teip_parametro/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Taxa_Teifa_Teip_Parametro.pdf</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip_parametro/DicionarioDados_Taxa_Teifa_Teip_Parametro.pdf</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:02</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>54bb6ffbccd9bc33bd4c4ce6e0c43adfed9313406dedefc79ff25fee62216fd6</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>195012</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>taxa_teif_teip_parametro</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>indicadores_ons/taxa_teif_teip_parametro/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Taxa_Teifa_Teip_Parametro.json</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip_parametro/DicionarioDados_Taxa_Teifa_Teip_Parametro.json</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:02</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>6c466a16a2d57ead6a423cb9c81cc756f9bc0aebfd46d6805a169f596e20efea</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>789</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0</v>
-      </c>
-      <c r="K7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>taxa_teif_teip</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>indicadores_ons/taxa_teif_teip/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Taxa_Teifa_Teip.pdf</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip/DicionarioDados_Taxa_Teifa_Teip.pdf</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:06</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2b9cee1c07cd18f3c645ed7397a95f0f6ae34359c80583b0b99d84d889488f49</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>175489</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>taxa_teif_teip</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>indicadores_ons/taxa_teif_teip/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Taxa_Teifa_Teip.json</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip/DicionarioDados_Taxa_Teifa_Teip.json</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:06</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>cf9115681fa52e0837a756845ae8b7cc525a724fdf6abb84f6f8335115f9b0ef</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>1089</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>programacao_diaria</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>programacao_diaria/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Valores_Programacao_Diaria.pdf</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/programacao_diaria/DicionarioDados_Valores_Programacao_Diaria.pdf</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:09</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>00d33b947e376732337be71b481b154edb77aa8011deb04f4b117e43b71deee6</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>145348</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>programacao_diaria</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>programacao_diaria/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Valores_Programacao_Diaria.json</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/programacao_diaria/DicionarioDados_Valores_Programacao_Diaria.json</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:09</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>3d78e62a8a83f00a3e8cb6435aed15ff22ba3bb995efa64ef01effbef3d540d3</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2817</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>disponibilidade_usina</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>disponibilidade_usina/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Disponibilidade_Usinas.pdf</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/disponibilidade_usina_ho/DicionarioDados_Disponibilidade_Usinas.pdf</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:15</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>371e7ee0daa72ae443259c2b43a42ef1637b636811eb4f8cc0f2af8e3583d9a7</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>131707</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>disponibilidade_usina</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>disponibilidade_usina/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Disponibilidade_Usinas.json</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/disponibilidade_usina_ho/DicionarioDados_Disponibilidade_Usinas.json</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:15</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>b81f3a7effb2e0195d1336e44823b39c81495e0e1ed40aa7f9b4239c3f4e6f4a</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1765</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>geracao-usina-2</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>geracao_usina_2/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DicionarioDados_GeracaoPorUsina.pdf</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_usina_2_ho/DicionarioDados_GeracaoPorUsina.pdf</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:19</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>c254f312198ad314bc9c142bf016351c90ffb3f384b9b6be88e3e19d61c6a78e</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>181813</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>geracao-usina-2</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>geracao_usina_2/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>DicionarioDados_GeracaoPorUsina.json</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_usina_2_ho/DicionarioDados_GeracaoPorUsina.json</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:19</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>5bc25c0f2d81371548fe9b23fb5b4ba61922755732291eca561ade07020640a3</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1508</v>
-      </c>
-      <c r="J15" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>modalidade-usina</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>modalidade_usina/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Modalidade_Operacao_Usina.pdf</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/modalidade_usina/DicionarioDados_Modalidade_Operacao_Usina.pdf</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:22</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>ddb185b6ca5579dbe324aae60e43e87cf14e7d49309ad880a14e8c64db8c277d</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>222137</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>modalidade-usina</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>modalidade_usina/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Modalidade_Operacao_Usina.json</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/modalidade_usina/DicionarioDados_Modalidade_Operacao_Usina.json</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:22</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>c8313e779e068745f70a5e096f820b29d61e06790a0790d9b04259ca72e4fc12</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1451</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>usina_conjunto</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>usina_conjunto/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Usina_Conjunto.pdf</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/usina_conjunto/DicionarioDados_Usina_Conjunto.pdf</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:26</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>72567e590a2d38686847e55a4520c5553d29d99e1235e835b360d1572457c0b3</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>184353</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>usina_conjunto</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>usina_conjunto/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Usina_Conjunto.json</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/usina_conjunto/DicionarioDados_Usina_Conjunto.json</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:26</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>8a294c3b918a70cacde8d2befa490c08a347af2ede4fe90141b7b1799223ff7d</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1952</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>capacidade-geracao</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>capacidade_geracao/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Capacidade_Instalada_Geracao.pdf</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/capacidade-geracao/DicionarioDados_Capacidade_Instalada_Geracao.pdf</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:28</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2f327d123f18a9fa76dedda048511206efd4a6b3ab8ec691e97f3365251f72d2</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>230482</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>capacidade-geracao</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>capacidade_geracao/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Capacidade_Instalada_Geracao.json</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/capacidade-geracao/DicionarioDados_Capacidade_Instalada_Geracao.json</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:28</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>68e823cd62cc06aeb2ccdcc261a53904edc36c9a08b97c75ed1c3e3d21faea17</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>2733</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>geracao-termica-despacho-2</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>geracao_termica_despacho_2/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.pdf</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_termica_despacho_2_ho/DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.pdf</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:31</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>d307e95f8df00d95508f038fbe8beaebc169491486cbaedfcd3f641ba4d678f8</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>377021</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>geracao-termica-despacho-2</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>geracao_termica_despacho_2/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.json</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_termica_despacho_2_ho/DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.json</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:31</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>f351c194e0812cf26b1f9fadd808bd30fd9d27dde230b09b00288914e18c65eb</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>9804</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>cvu-usitermica</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>cvu_usitermica/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>DicionarioDados_CVU_UsinaTermica.pdf</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cvu_usitermica_se/DicionarioDados_CVU_UsinaTermica.pdf</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:35</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>312d61cd253e087d1bc1ccbc5a8593cd1518c76b60521d70c16a736cd592a105</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>183848</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>cvu-usitermica</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>cvu_usitermica/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>DicionarioDados_CVU_UsinaTermica.json</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cvu_usitermica_se/DicionarioDados_CVU_UsinaTermica.json</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>INALTERADO</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:35</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>4a0d91862ad7e14cbd461e357765a4fc6698b38d5b23d28ba6ead5888238e90f</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1129</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>cmo-semanal</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>cmo_semanal/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PDF</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Cmo_Semanal.pdf</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cmo_se/DicionarioDados_Cmo_Semanal.pdf</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>NOVO</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:38</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>7fbeab4ceadbf16e9e11c8f73df2b112e765890742067a6985f2a14277bc81eb</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>171054</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cmo-semanal</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>cmo_semanal/_dicionarios</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>DicionarioDados_Cmo_Semanal.json</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cmo_se/DicionarioDados_Cmo_Semanal.json</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>NOVO</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>2026-10-20 12:10:38</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>64dd2cc177643a3a42f0b15c3e748cc54f463d73a1cb2b17c27f927c57ded4b9</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>964</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -72277,16 +72411,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>432</v>
+        <v>576</v>
       </c>
       <c r="D65" t="n">
-        <v>432</v>
+        <v>576</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9212395833333333</v>
+        <v>1.967263020833333</v>
       </c>
       <c r="F65" t="n">
-        <v>397.9755</v>
+        <v>1133.1435</v>
       </c>
     </row>
   </sheetData>
@@ -72300,7 +72434,1463 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:K29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="28" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
+    <col width="25" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>conjunto</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>pasta</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>formato</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>arquivo</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>url</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>resultado_ultima_obtencao</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>obtido_em_utc</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sha256</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>tamanho_bytes</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>versoes_anteriores</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>ultima_versao_anterior</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>ind_disponibilidade_fgeracao_uge_mensal</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_mensal/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.pdf</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_me/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:35</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9a7e03afa6c275128c94534ddb28d8608e6c79dd7915f5ca213f21cda6ea7a09</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>306461</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ind_disponibilidade_fgeracao_uge_mensal</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_mensal/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.json</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_me/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Mensal.json</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:35</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>8e4e092e95f037007a5d78adae5562487f63752db6bc4cf21f03ba0b2e98cac1</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>3367</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ind_disponibilidade_fgeracao_uge_anual</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_anual/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.pdf</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_an/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.pdf</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:38</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>344bf26d186b570cf2715f4389cc0928d184d58ff02fa7b72e299a1716b4bcdb</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>308635</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>ind_disponibilidade_fgeracao_uge_anual</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>indicadores_ons/ind_disponibilidade_fgeracao_uge_anual/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.json</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/ind_disponibilidade_fgeracao_uge_an/DicionarioDados_Ind_Disponibilidade_FuncaoGeracao_UGE_Anual.json</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:38</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>4c876daff676113179e80378f9e473e124d50a34e216d1e4ac5b33102612b431</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>3355</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>taxa_teif_teip_parametro</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>indicadores_ons/taxa_teif_teip_parametro/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Taxa_Teifa_Teip_Parametro.pdf</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip_parametro/DicionarioDados_Taxa_Teifa_Teip_Parametro.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:41</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>54bb6ffbccd9bc33bd4c4ce6e0c43adfed9313406dedefc79ff25fee62216fd6</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>195012</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>taxa_teif_teip_parametro</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>indicadores_ons/taxa_teif_teip_parametro/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Taxa_Teifa_Teip_Parametro.json</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip_parametro/DicionarioDados_Taxa_Teifa_Teip_Parametro.json</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:41</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>6c466a16a2d57ead6a423cb9c81cc756f9bc0aebfd46d6805a169f596e20efea</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>789</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>taxa_teif_teip</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>indicadores_ons/taxa_teif_teip/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Taxa_Teifa_Teip.pdf</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip/DicionarioDados_Taxa_Teifa_Teip.pdf</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:44</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2b9cee1c07cd18f3c645ed7397a95f0f6ae34359c80583b0b99d84d889488f49</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>175489</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>taxa_teif_teip</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>indicadores_ons/taxa_teif_teip/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Taxa_Teifa_Teip.json</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip/DicionarioDados_Taxa_Teifa_Teip.json</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:44</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>cf9115681fa52e0837a756845ae8b7cc525a724fdf6abb84f6f8335115f9b0ef</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1089</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>taxa_teif_teip_oper</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>indicadores_ons/taxa_teif_teip_oper/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Taxa_Teifa_Teip_Oper.pdf</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip_oper/DicionarioDados_Taxa_Teifa_Teip_Oper.pdf</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:47</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2946160255839466ad17ca511c0f28c682535dd7ea205370742b751b1f4b3170</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>130911</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>taxa_teif_teip_oper</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>indicadores_ons/taxa_teif_teip_oper/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Taxa_Teifa_Teip_Oper.json</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/taxa_teif_teip_oper/DicionarioDados_Taxa_Teifa_Teip_Oper.json</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:47</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>a9ba9637ce8471a7570084cf3af2e4656ca6407b098be318cbee4d49f97d9d62</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1104</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>programacao_diaria</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>programacao_diaria/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Valores_Programacao_Diaria.pdf</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/programacao_diaria/DicionarioDados_Valores_Programacao_Diaria.pdf</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:50</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>00d33b947e376732337be71b481b154edb77aa8011deb04f4b117e43b71deee6</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>145348</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>programacao_diaria</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>programacao_diaria/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Valores_Programacao_Diaria.json</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/programacao_diaria/DicionarioDados_Valores_Programacao_Diaria.json</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:50</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>3d78e62a8a83f00a3e8cb6435aed15ff22ba3bb995efa64ef01effbef3d540d3</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2817</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>disponibilidade_usina</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>disponibilidade_usina/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Disponibilidade_Usinas.pdf</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/disponibilidade_usina_ho/DicionarioDados_Disponibilidade_Usinas.pdf</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:56</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>371e7ee0daa72ae443259c2b43a42ef1637b636811eb4f8cc0f2af8e3583d9a7</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>131707</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>disponibilidade_usina</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>disponibilidade_usina/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Disponibilidade_Usinas.json</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/disponibilidade_usina_ho/DicionarioDados_Disponibilidade_Usinas.json</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:23:56</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>b81f3a7effb2e0195d1336e44823b39c81495e0e1ed40aa7f9b4239c3f4e6f4a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1765</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>geracao-usina-2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>geracao_usina_2/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>DicionarioDados_GeracaoPorUsina.pdf</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_usina_2_ho/DicionarioDados_GeracaoPorUsina.pdf</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:24:04</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>c254f312198ad314bc9c142bf016351c90ffb3f384b9b6be88e3e19d61c6a78e</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>181813</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>geracao-usina-2</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>geracao_usina_2/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>DicionarioDados_GeracaoPorUsina.json</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_usina_2_ho/DicionarioDados_GeracaoPorUsina.json</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:24:04</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>5bc25c0f2d81371548fe9b23fb5b4ba61922755732291eca561ade07020640a3</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1508</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>modalidade-usina</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>modalidade_usina/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Modalidade_Operacao_Usina.pdf</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/modalidade_usina/DicionarioDados_Modalidade_Operacao_Usina.pdf</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:24:07</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>ddb185b6ca5579dbe324aae60e43e87cf14e7d49309ad880a14e8c64db8c277d</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>222137</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>modalidade-usina</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>modalidade_usina/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Modalidade_Operacao_Usina.json</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/modalidade_usina/DicionarioDados_Modalidade_Operacao_Usina.json</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026-10-26 12:24:07</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>c8313e779e068745f70a5e096f820b29d61e06790a0790d9b04259ca72e4fc12</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1451</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>usina_conjunto</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>usina_conjunto/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Usina_Conjunto.pdf</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/usina_conjunto/DicionarioDados_Usina_Conjunto.pdf</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:30</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>72567e590a2d38686847e55a4520c5553d29d99e1235e835b360d1572457c0b3</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>184353</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>usina_conjunto</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>usina_conjunto/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Usina_Conjunto.json</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/usina_conjunto/DicionarioDados_Usina_Conjunto.json</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:30</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>8a294c3b918a70cacde8d2befa490c08a347af2ede4fe90141b7b1799223ff7d</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1952</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>capacidade-geracao</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>capacidade_geracao/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Capacidade_Instalada_Geracao.pdf</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/capacidade-geracao/DicionarioDados_Capacidade_Instalada_Geracao.pdf</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:34</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2f327d123f18a9fa76dedda048511206efd4a6b3ab8ec691e97f3365251f72d2</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>230482</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>capacidade-geracao</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>capacidade_geracao/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Capacidade_Instalada_Geracao.json</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/capacidade-geracao/DicionarioDados_Capacidade_Instalada_Geracao.json</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026-10-22 12:58:34</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>68e823cd62cc06aeb2ccdcc261a53904edc36c9a08b97c75ed1c3e3d21faea17</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>2733</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>geracao-termica-despacho-2</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>geracao_termica_despacho_2/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.pdf</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_termica_despacho_2_ho/DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.pdf</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:48:52</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>d307e95f8df00d95508f038fbe8beaebc169491486cbaedfcd3f641ba4d678f8</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>377021</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>geracao-termica-despacho-2</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>geracao_termica_despacho_2/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.json</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/geracao_termica_despacho_2_ho/DicionarioDados_Geracao_Termica_Por_Motivo_Despacho.json</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:48:52</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>f351c194e0812cf26b1f9fadd808bd30fd9d27dde230b09b00288914e18c65eb</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>9804</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cvu-usitermica</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cvu_usitermica/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>DicionarioDados_CVU_UsinaTermica.pdf</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cvu_usitermica_se/DicionarioDados_CVU_UsinaTermica.pdf</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:48:56</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>312d61cd253e087d1bc1ccbc5a8593cd1518c76b60521d70c16a736cd592a105</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>183848</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cvu-usitermica</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>cvu_usitermica/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>DicionarioDados_CVU_UsinaTermica.json</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cvu_usitermica_se/DicionarioDados_CVU_UsinaTermica.json</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>INALTERADO</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026-10-21 12:48:56</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>4a0d91862ad7e14cbd461e357765a4fc6698b38d5b23d28ba6ead5888238e90f</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1129</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cmo-semanal</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>cmo_semanal/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PDF</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Cmo_Semanal.pdf</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cmo_se/DicionarioDados_Cmo_Semanal.pdf</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:10:38</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>7fbeab4ceadbf16e9e11c8f73df2b112e765890742067a6985f2a14277bc81eb</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>171054</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cmo-semanal</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>cmo_semanal/_dicionarios</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>DicionarioDados_Cmo_Semanal.json</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>https://ons-aws-prod-opendata.s3.amazonaws.com/dataset/cmo_se/DicionarioDados_Cmo_Semanal.json</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>NOVO</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-10-20 12:10:38</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>64dd2cc177643a3a42f0b15c3e748cc54f463d73a1cb2b17c27f927c57ded4b9</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>964</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -72345,12 +73935,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Programação diária (MSUTWI), obtido em 20/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.760 de 5.760 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -72372,12 +73962,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Programação diária (MSUTWI), obtido em 20/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.760 de 5.760 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -72399,7 +73989,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -72426,7 +74016,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -72453,7 +74043,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -72480,7 +74070,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -72507,7 +74097,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -72534,7 +74124,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -72561,7 +74151,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -72642,7 +74232,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (id ONS MSUTWI), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Programação diária (MSUTWI), obtido em 20/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -72669,7 +74259,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -72696,7 +74286,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -72723,7 +74313,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -72750,7 +74340,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Programação diária (MSUTWI), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Programação diária (MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -72777,7 +74367,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Programação diária (MSUTWI), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Programação diária (MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -72804,12 +74394,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -72831,12 +74421,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -72858,7 +74448,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -72885,12 +74475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.760 de 5.760 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -72912,12 +74502,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.760 de 5.760 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -72939,12 +74529,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -72966,12 +74556,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -72993,7 +74583,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -73020,7 +74610,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -73047,12 +74637,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Programação diária (MSUTWI), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026</t>
+          <t>Programação diária (MSUTWI), obtido em 26/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.760 de 5.760 horas coincidentes (100,0%)</t>
+          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -73074,12 +74664,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -73101,12 +74691,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.121 de 46.243 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -73128,7 +74718,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -73155,7 +74745,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -73182,7 +74772,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -73209,7 +74799,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -73236,7 +74826,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -73263,7 +74853,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -73285,17 +74875,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ONS_DIVERGENCIAS</t>
+          <t>ONS_TAXAS_OPERATIVAS</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS</t>
+          <t>—</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -73305,24 +74895,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>não</t>
+          <t>sim</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CAD_FICHA</t>
+          <t>ONS_DIVERGENCIAS</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência</t>
+          <t>DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -73339,17 +74929,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CAD_AUDITORIA</t>
+          <t>CAD_FICHA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026</t>
+          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -73366,25 +74956,52 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>CAD_AUDITORIA</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>DICIONARIOS</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Programação diária (MSUTWI), obtido em 20/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 20/10/2026; Geração por usina (id ONS MSUTWI), obtido em 20/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS ), data de obtenção não registrada; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 20/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS ), data de obtenção não registrada; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>não</t>
         </is>
@@ -73586,7 +75203,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.51372290462428</v>
+        <v>19.03076012569833</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -73676,10 +75293,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.628357031655423</v>
+        <v>6.608160113812726</v>
       </c>
       <c r="D2" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="3">
@@ -73692,10 +75309,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.571929942916451</v>
+        <v>6.551910501810657</v>
       </c>
       <c r="D3" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="4">
@@ -73708,10 +75325,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.54437415672029</v>
+        <v>6.524426539058458</v>
       </c>
       <c r="D4" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="5">
@@ -73724,10 +75341,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.58592471443406</v>
+        <v>6.56585248447205</v>
       </c>
       <c r="D5" t="n">
-        <v>1926</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="6">
@@ -73740,10 +75357,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.625573430202387</v>
+        <v>6.605391619244697</v>
       </c>
       <c r="D6" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="7">
@@ -73756,10 +75373,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.695992211838006</v>
+        <v>6.675572463768116</v>
       </c>
       <c r="D7" t="n">
-        <v>1926</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="8">
@@ -73772,10 +75389,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.675085625324338</v>
+        <v>6.65474236937403</v>
       </c>
       <c r="D8" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="9">
@@ -73788,10 +75405,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.726391281785158</v>
+        <v>6.705889032591826</v>
       </c>
       <c r="D9" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="10">
@@ -73804,10 +75421,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.568381940840686</v>
+        <v>6.548368339368857</v>
       </c>
       <c r="D10" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="11">
@@ -73820,10 +75437,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.3916388168137</v>
+        <v>6.372177444386963</v>
       </c>
       <c r="D11" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="12">
@@ -73836,10 +75453,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.156532952776335</v>
+        <v>6.137781427832385</v>
       </c>
       <c r="D12" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="13">
@@ -73852,10 +75469,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.104719252724442</v>
+        <v>6.086363683393689</v>
       </c>
       <c r="D13" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="14">
@@ -73868,10 +75485,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.095039958484691</v>
+        <v>6.07680703569581</v>
       </c>
       <c r="D14" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="15">
@@ -73884,10 +75501,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.989123508043591</v>
+        <v>5.97120563890326</v>
       </c>
       <c r="D15" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="16">
@@ -73900,10 +75517,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.982303219106957</v>
+        <v>5.964300207039337</v>
       </c>
       <c r="D16" t="n">
-        <v>1926</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="17">
@@ -73916,10 +75533,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.976988577362409</v>
+        <v>5.959044254658385</v>
       </c>
       <c r="D17" t="n">
-        <v>1926</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="18">
@@ -73932,10 +75549,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.083448624805397</v>
+        <v>6.075216502845318</v>
       </c>
       <c r="D18" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="19">
@@ -73948,10 +75565,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.629913855734301</v>
+        <v>6.639949301603726</v>
       </c>
       <c r="D19" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="20">
@@ -73964,10 +75581,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.099337830825117</v>
+        <v>7.14187247801345</v>
       </c>
       <c r="D20" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="21">
@@ -73980,10 +75597,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.416324766355141</v>
+        <v>7.458722567287785</v>
       </c>
       <c r="D21" t="n">
-        <v>1926</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="22">
@@ -73996,10 +75613,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.5631658017644</v>
+        <v>7.599786601138128</v>
       </c>
       <c r="D22" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="23">
@@ -74012,10 +75629,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.555222106901921</v>
+        <v>7.581912829798241</v>
       </c>
       <c r="D23" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="24">
@@ -74028,10 +75645,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.459367929423975</v>
+        <v>7.500553802379721</v>
       </c>
       <c r="D24" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
     <row r="25">
@@ -74044,10 +75661,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.076681110534509</v>
+        <v>7.081958872219348</v>
       </c>
       <c r="D25" t="n">
-        <v>1927</v>
+        <v>1933</v>
       </c>
     </row>
   </sheetData>
@@ -74098,7 +75715,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1322</v>
+        <v>1320</v>
       </c>
     </row>
   </sheetData>
@@ -74378,7 +75995,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-18 23:00:00</t>
+          <t>2026-10-24 23:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">

--- a/reports/william_arjona/perfil_estatistico_anual.xlsx
+++ b/reports/william_arjona/perfil_estatistico_anual.xlsx
@@ -484,7 +484,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Série de referência: Geração por usina (id ONS MSUTWI), de 10/07/2021 00h a 24/10/2026 23h: 46.387 horas com registro de 46.392 no período (99,99%). 5 horas ausentes, listadas na planilha, sem preenchimento. O período tem 3 trechos, com mudança de modalidade, de composição do conjunto ou de código.</t>
+          <t>Série de referência: Geração por usina (id ONS MSUTWI), de 10/07/2021 00h a 27/10/2026 23h: 46.459 horas com registro de 46.464 no período (99,99%). 5 horas ausentes, listadas na planilha, sem preenchimento. O período tem 3 trechos, com mudança de modalidade, de composição do conjunto ou de código.</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geração média de 6,6 MWmed nas 46.387 horas com valor (307.484 MWh); geração até 1 MW em 92,8% das horas; entre os anos completos, maior média em 2022 (0,6 MWmed) e menor em 2023 (0,0 MWmed).</t>
+          <t>Geração média de 6,7 MWmed nas 46.459 horas com valor (309.146 MWh); geração até 1 MW em 92,8% das horas; entre os anos completos, maior média em 2022 (0,6 MWmed) e menor em 2023 (0,0 MWmed).</t>
         </is>
       </c>
     </row>
@@ -508,7 +508,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Disponibilidade operacional média de 38,8 MW (21,9% da potência instalada) e sincronizada de 7,0 MW, nas 46.387 horas com o dado; indisponibilidade total em 32.140 horas (22 eventos); geração acima da disponibilidade declarada em 1.320 horas.</t>
+          <t>Disponibilidade operacional média de 39,0 MW (22,0% da potência instalada) e sincronizada de 7,0 MW, nas 46.459 horas com o dado; indisponibilidade total em 32.140 horas (22 eventos); geração acima da disponibilidade declarada em 1.331 horas.</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nas 5.880 horas com programação e geração verificada, geração verificada média de 1,7 MW e programada de 2,1 MW (desvio médio absoluto de 0,8 MW; correlação de 0,93); 2 horas com geração até 1 MW e programação acima de 5 MW.</t>
+          <t>Nas 5.976 horas com programação e geração verificada, geração verificada média de 1,9 MW e programada de 2,0 MW (desvio médio absoluto de 1,0 MW; correlação de 0,84); 2 horas com geração até 1 MW e programação acima de 5 MW.</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geração verificada do despacho de 305.063 MWh de 10/07/2021 a 19/10/2026 (unidades de planejamento 334 e 434); geração programada em 3.271 horas. Maior motivo verificado: garantia energética, com 69,5% da geração verificada.</t>
+          <t>Geração verificada do despacho de 306.754 MWh de 10/07/2021 a 27/10/2026 (unidades de planejamento 334 e 434); geração programada em 3.271 horas. Maior motivo verificado: garantia energética, com 69,1% da geração verificada.</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nas 3.271 horas com geração programada, a verificada ficou mais de 5 MW abaixo da programada em 2.826 horas (112.445 MWh) e acima em 88 horas (1.875 MWh); sem programação, geração acima de 5 MW em 114 horas.</t>
+          <t>Nas 3.271 horas com geração programada, a verificada ficou mais de 5 MW abaixo da programada em 2.825 horas (112.414 MWh) e acima em 87 horas (1.825 MWh); sem programação, geração acima de 5 MW em 129 horas.</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Disponível, sem programação e sem geração em 10.873 das 46.267 horas com a disponibilidade e o despacho (23,5%), com a potência disponível média de 134,4 MW.</t>
+          <t>Disponível, sem programação e sem geração em 11.050 das 46.459 horas com a disponibilidade e o despacho (23,8%), com a potência disponível média de 134,7 MW.</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unidade 334: CVU abaixo do CMO em 4 e acima em 154 das 274 semanas; unidade 434: CVU abaixo do CMO em 0 e acima em 17 das 267 semanas; nas semanas com algum CVU abaixo do CMO, 0 horas disponíveis sem despacho.</t>
+          <t>Unidade 334: CVU abaixo do CMO em 4 e acima em 155 das 275 semanas; unidade 434: CVU abaixo do CMO em 0 e acima em 17 das 268 semanas; nas semanas com algum CVU abaixo do CMO, 0 horas disponíveis sem despacho.</t>
         </is>
       </c>
     </row>
@@ -580,7 +580,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.320 horas sinalizadas (2,85% das horas; R7, geração acima da disponibilidade declarada: 1.320 h), mantidas na base e nos totais.</t>
+          <t>1.331 horas sinalizadas (2,86% das horas; R7, geração acima da disponibilidade declarada: 1.331 h), mantidas na base e nos totais.</t>
         </is>
       </c>
     </row>
@@ -3496,31 +3496,31 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="C65" t="n">
-        <v>152.7156835815469</v>
+        <v>151.9807936619923</v>
       </c>
       <c r="D65" t="n">
-        <v>1.635416105416667</v>
+        <v>2.594950906975309</v>
       </c>
       <c r="E65" t="n">
-        <v>1.967263020833333</v>
+        <v>4.312550154320987</v>
       </c>
       <c r="F65" t="n">
-        <v>151.0802674761302</v>
+        <v>149.385842755017</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>561</v>
+        <v>618</v>
       </c>
       <c r="I65" t="n">
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -3820,37 +3820,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7123</v>
+        <v>7195</v>
       </c>
       <c r="C7" t="n">
-        <v>142.1991521047253</v>
+        <v>142.2382044464153</v>
       </c>
       <c r="D7" t="n">
-        <v>4.145949670731012</v>
+        <v>4.207245033442251</v>
       </c>
       <c r="E7" t="n">
-        <v>1.507440263933736</v>
+        <v>1.723264211257818</v>
       </c>
       <c r="F7" t="n">
-        <v>138.0532024339942</v>
+        <v>138.030959412973</v>
       </c>
       <c r="G7" t="n">
         <v>190</v>
       </c>
       <c r="H7" t="n">
-        <v>6793</v>
+        <v>6850</v>
       </c>
       <c r="I7" t="n">
         <v>482</v>
       </c>
       <c r="J7" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="K7" t="b">
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>80.28588727428649</v>
+        <v>80.30793629396288</v>
       </c>
     </row>
   </sheetData>
@@ -4452,19 +4452,19 @@
         <v>46296</v>
       </c>
       <c r="B10" t="n">
-        <v>552</v>
+        <v>648</v>
       </c>
       <c r="C10" t="n">
-        <v>2.025172101449275</v>
+        <v>4.312550154320987</v>
       </c>
       <c r="D10" t="n">
-        <v>3.504528985507247</v>
+        <v>2.985339506172839</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.479356884057971</v>
+        <v>1.327210648148148</v>
       </c>
       <c r="F10" t="n">
-        <v>1.704596014492753</v>
+        <v>3.997826388888889</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -6117,7 +6117,7 @@
         <v>13746</v>
       </c>
       <c r="E57" t="n">
-        <v>10707.578</v>
+        <v>12398.885</v>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
@@ -6148,7 +6148,7 @@
         <v>42.67059508220573</v>
       </c>
       <c r="G58" t="n">
-        <v>39.09054876835826</v>
+        <v>33.75828552325471</v>
       </c>
     </row>
     <row r="59">
@@ -6171,13 +6171,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="n">
-        <v>985.0549999999999</v>
+        <v>1018.118</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>9.199606110737648</v>
+        <v>8.211367393116397</v>
       </c>
     </row>
     <row r="60">
@@ -6200,13 +6200,13 @@
         <v>3587</v>
       </c>
       <c r="E60" t="n">
-        <v>2225.974</v>
+        <v>3871.83</v>
       </c>
       <c r="F60" t="n">
         <v>26.09486396042485</v>
       </c>
       <c r="G60" t="n">
-        <v>20.78877221347349</v>
+        <v>31.22724341745246</v>
       </c>
     </row>
     <row r="61">
@@ -6258,13 +6258,13 @@
         <v>4293.5</v>
       </c>
       <c r="E62" t="n">
-        <v>3310.907</v>
+        <v>3323.295</v>
       </c>
       <c r="F62" t="n">
         <v>31.23454095736942</v>
       </c>
       <c r="G62" t="n">
-        <v>30.92115696005203</v>
+        <v>26.80317625334859</v>
       </c>
     </row>
     <row r="63">
@@ -6287,13 +6287,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="n">
-        <v>973.116</v>
+        <v>1006.179</v>
       </c>
       <c r="F63" t="n">
         <v>0</v>
       </c>
       <c r="G63" t="n">
-        <v>9.088105638828875</v>
+        <v>8.115076476634794</v>
       </c>
     </row>
     <row r="64">
@@ -6322,7 +6322,7 @@
         <v>0</v>
       </c>
       <c r="G64" t="n">
-        <v>0.1115004719087734</v>
+        <v>0.096290916481603</v>
       </c>
     </row>
     <row r="65">
@@ -6351,7 +6351,7 @@
         <v>42.67059508220573</v>
       </c>
       <c r="G65" t="n">
-        <v>39.09054876835826</v>
+        <v>33.75828552325471</v>
       </c>
     </row>
     <row r="66">
@@ -6405,7 +6405,7 @@
         <v>20.64600611086862</v>
       </c>
       <c r="G67" t="n">
-        <v>20.98984476227957</v>
+        <v>18.12666219583455</v>
       </c>
     </row>
   </sheetData>
@@ -24195,7 +24195,7 @@
         <v>1934.5</v>
       </c>
       <c r="E695" t="n">
-        <v>1103.228</v>
+        <v>2794.535</v>
       </c>
       <c r="F695" t="inlineStr"/>
       <c r="G695" t="inlineStr"/>
@@ -24249,13 +24249,13 @@
         <v>0</v>
       </c>
       <c r="E697" t="n">
-        <v>16.94</v>
+        <v>50.003</v>
       </c>
       <c r="F697" t="n">
         <v>0</v>
       </c>
       <c r="G697" t="n">
-        <v>1.53549402299434</v>
+        <v>1.789313785656648</v>
       </c>
     </row>
     <row r="698">
@@ -24278,13 +24278,13 @@
         <v>1504.5</v>
       </c>
       <c r="E698" t="n">
-        <v>794.693</v>
+        <v>2440.549</v>
       </c>
       <c r="F698" t="n">
         <v>77.77203411734298</v>
       </c>
       <c r="G698" t="n">
-        <v>72.03343279902251</v>
+        <v>87.3329194302451</v>
       </c>
     </row>
     <row r="699">
@@ -24336,13 +24336,13 @@
         <v>430</v>
       </c>
       <c r="E700" t="n">
-        <v>291.595</v>
+        <v>303.983</v>
       </c>
       <c r="F700" t="n">
         <v>22.22796588265702</v>
       </c>
       <c r="G700" t="n">
-        <v>26.43107317798315</v>
+        <v>10.87776678409825</v>
       </c>
     </row>
     <row r="701">
@@ -24365,13 +24365,13 @@
         <v>0</v>
       </c>
       <c r="E701" t="n">
-        <v>16.94</v>
+        <v>50.003</v>
       </c>
       <c r="F701" t="n">
         <v>0</v>
       </c>
       <c r="G701" t="n">
-        <v>1.53549402299434</v>
+        <v>1.789313785656648</v>
       </c>
     </row>
     <row r="702">
@@ -24550,7 +24550,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Geração acima da disponibilidade declarada em 1.320 h, segundo a regra R7</t>
+          <t>Geração acima da disponibilidade declarada em 1.331 h, segundo a regra R7</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -24575,7 +24575,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.826 h (112.445 MWh)</t>
+          <t>Geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.825 h (112.414 MWh)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -24600,7 +24600,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Critério e horário da declaração de disponibilidade ao ONS, dado que a geração superou a disponibilidade declarada em 1.320 h</t>
+          <t>Critério e horário da declaração de disponibilidade ao ONS, dado que a geração superou a disponibilidade declarada em 1.331 h</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -24650,7 +24650,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Motivo da geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.826 h (112.445 MWh)</t>
+          <t>Motivo da geração verificada mais de 5 MW abaixo da programada pelo ONS em 2.825 h (112.414 MWh)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -24675,7 +24675,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Programação do ONS correspondente à geração verificada em 114 h sem programação, com 3.028 MWh acima da programada</t>
+          <t>Programação do ONS correspondente à geração verificada em 129 h sem programação, com 4.739 MWh acima da programada</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -25666,7 +25666,7 @@
         <v>0</v>
       </c>
       <c r="C65" t="n">
-        <v>16.94</v>
+        <v>50.003</v>
       </c>
       <c r="D65" t="n">
         <v>0</v>
@@ -25876,22 +25876,22 @@
         <v>118</v>
       </c>
       <c r="C7" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D7" t="n">
-        <v>3988.218</v>
+        <v>3957.748</v>
       </c>
       <c r="E7" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F7" t="n">
-        <v>312.306</v>
+        <v>262.044</v>
       </c>
       <c r="G7" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="H7" t="n">
-        <v>615.484</v>
+        <v>2326.508</v>
       </c>
     </row>
   </sheetData>
@@ -26628,10 +26628,10 @@
         <v>46296</v>
       </c>
       <c r="B65" t="n">
-        <v>895.159</v>
+        <v>864.689</v>
       </c>
       <c r="C65" t="n">
-        <v>63.887</v>
+        <v>13.625</v>
       </c>
     </row>
   </sheetData>
@@ -27001,13 +27001,13 @@
         <v>2026</v>
       </c>
       <c r="B7" t="n">
-        <v>7003</v>
+        <v>7195</v>
       </c>
       <c r="C7" t="n">
-        <v>6671</v>
+        <v>6848</v>
       </c>
       <c r="D7" t="n">
-        <v>146.2460621641228</v>
+        <v>146.4191170702195</v>
       </c>
     </row>
   </sheetData>
@@ -27021,7 +27021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I542"/>
+  <dimension ref="A1:I544"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -44134,7 +44134,7 @@
         </is>
       </c>
       <c r="H539" t="n">
-        <v>397.976</v>
+        <v>404.035</v>
       </c>
       <c r="I539" t="n">
         <v>160</v>
@@ -44196,10 +44196,10 @@
         </is>
       </c>
       <c r="H541" t="n">
-        <v>705.252</v>
+        <v>679.476</v>
       </c>
       <c r="I541" t="n">
-        <v>65</v>
+        <v>161</v>
       </c>
     </row>
     <row r="542">
@@ -44232,7 +44232,69 @@
         <v>0</v>
       </c>
       <c r="I542" t="n">
-        <v>65</v>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="n">
+        <v>334</v>
+      </c>
+      <c r="B543" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C543" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D543" t="n">
+        <v>2066.66</v>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>acima</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>1711.024</v>
+      </c>
+      <c r="I543" t="n">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="n">
+        <v>434</v>
+      </c>
+      <c r="B544" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="C544" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="D544" t="n">
+        <v>0</v>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>zero</t>
+        </is>
+      </c>
+      <c r="F544" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>sem comparação</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>0</v>
+      </c>
+      <c r="I544" t="n">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -44312,7 +44374,7 @@
         <v>334</v>
       </c>
       <c r="B2" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C2" t="n">
         <v>4</v>
@@ -44321,10 +44383,10 @@
         <v>66404.97400000002</v>
       </c>
       <c r="E2" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F2" t="n">
-        <v>84590.0435</v>
+        <v>86281.3505</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -44341,7 +44403,7 @@
         <v>434</v>
       </c>
       <c r="B3" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -44359,10 +44421,10 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="I3" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -46211,13 +46273,13 @@
         <v>0</v>
       </c>
       <c r="E65" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="F65" t="n">
         <v>0</v>
       </c>
       <c r="G65" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -48060,25 +48122,25 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1103.228</v>
+        <v>2794.535</v>
       </c>
       <c r="C65" t="n">
-        <v>1109.2865</v>
+        <v>2794.5325</v>
       </c>
       <c r="D65" t="n">
-        <v>-6.058499999999867</v>
+        <v>0.00250000000005457</v>
       </c>
       <c r="E65" t="n">
-        <v>456</v>
+        <v>648</v>
       </c>
       <c r="F65" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -48092,7 +48154,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -48297,23 +48359,6 @@
       </c>
       <c r="E11" t="n">
         <v>0.2000000000000028</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="n">
-        <v>46310.66666666666</v>
-      </c>
-      <c r="B12" s="1" t="n">
-        <v>46310.95833333334</v>
-      </c>
-      <c r="C12" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" t="n">
-        <v>12.8486875</v>
-      </c>
-      <c r="E12" t="n">
-        <v>32.777</v>
       </c>
     </row>
   </sheetData>
@@ -48630,32 +48675,32 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>7123</v>
+        <v>7195</v>
       </c>
       <c r="E7" t="n">
-        <v>7123</v>
+        <v>7195</v>
       </c>
       <c r="F7" t="n">
-        <v>1.507440263933736</v>
+        <v>1.723264211257818</v>
       </c>
       <c r="G7" t="n">
-        <v>10737.497</v>
+        <v>12398.886</v>
       </c>
       <c r="H7" t="n">
-        <v>154.712</v>
+        <v>157.8615</v>
       </c>
       <c r="I7" t="n">
-        <v>6983</v>
+        <v>7040</v>
       </c>
       <c r="J7" t="n">
-        <v>98.0345360101081</v>
+        <v>97.84572619874913</v>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="n">
-        <v>142.1991521047252</v>
+        <v>142.2382044464152</v>
       </c>
       <c r="M7" t="n">
-        <v>80.28588727428647</v>
+        <v>80.30793629396284</v>
       </c>
     </row>
   </sheetData>
@@ -48831,7 +48876,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="n">
-        <v>80.28588727428647</v>
+        <v>80.30793629396284</v>
       </c>
       <c r="D7" t="n">
         <v>99.14499062125448</v>
@@ -70837,7 +70882,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:31</t>
+          <t>2026-10-29 14:16:36</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -70940,7 +70985,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6034</v>
+        <v>6048</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -72411,16 +72456,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="D65" t="n">
-        <v>576</v>
+        <v>648</v>
       </c>
       <c r="E65" t="n">
-        <v>1.967263020833333</v>
+        <v>4.312550154320987</v>
       </c>
       <c r="F65" t="n">
-        <v>1133.1435</v>
+        <v>2794.5325</v>
       </c>
     </row>
   </sheetData>
@@ -72540,7 +72585,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:35</t>
+          <t>2026-10-29 14:53:59</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -72589,7 +72634,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:35</t>
+          <t>2026-10-29 14:53:59</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -72638,7 +72683,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:38</t>
+          <t>2026-10-29 14:54:02</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -72687,7 +72732,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:38</t>
+          <t>2026-10-29 14:54:02</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -72736,7 +72781,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:41</t>
+          <t>2026-10-29 14:54:05</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -72785,7 +72830,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:41</t>
+          <t>2026-10-29 14:54:05</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -72834,7 +72879,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:44</t>
+          <t>2026-10-29 14:54:08</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -72883,7 +72928,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:44</t>
+          <t>2026-10-29 14:54:08</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -72927,12 +72972,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>INALTERADO</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:47</t>
+          <t>2026-10-29 14:54:10</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -72976,12 +73021,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NOVO</t>
+          <t>INALTERADO</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:47</t>
+          <t>2026-10-29 14:54:10</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -73030,7 +73075,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:50</t>
+          <t>2026-10-29 15:00:41</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -73079,7 +73124,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:50</t>
+          <t>2026-10-29 15:00:41</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -73128,7 +73173,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:56</t>
+          <t>2026-10-29 14:54:16</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -73177,7 +73222,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-26 12:23:56</t>
+          <t>2026-10-29 14:54:16</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -73226,7 +73271,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-26 12:24:04</t>
+          <t>2026-10-29 15:00:45</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -73275,7 +73320,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-26 12:24:04</t>
+          <t>2026-10-29 15:00:45</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -73324,7 +73369,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-26 12:24:07</t>
+          <t>2026-10-29 15:00:48</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -73373,7 +73418,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-26 12:24:07</t>
+          <t>2026-10-29 15:00:48</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -73422,7 +73467,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:30</t>
+          <t>2026-10-29 15:00:50</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -73471,7 +73516,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:30</t>
+          <t>2026-10-29 15:00:50</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -73520,7 +73565,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:34</t>
+          <t>2026-10-29 15:00:53</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -73569,7 +73614,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-22 12:58:34</t>
+          <t>2026-10-29 15:00:53</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -73618,7 +73663,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-21 12:48:52</t>
+          <t>2026-10-29 14:54:30</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -73667,7 +73712,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-21 12:48:52</t>
+          <t>2026-10-29 14:54:30</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -73716,7 +73761,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-21 12:48:56</t>
+          <t>2026-10-29 14:54:34</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -73765,7 +73810,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-21 12:48:56</t>
+          <t>2026-10-29 14:54:34</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -73814,7 +73859,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-20 12:10:38</t>
+          <t>2026-10-29 14:54:36</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -73863,7 +73908,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-20 12:10:38</t>
+          <t>2026-10-29 14:54:36</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -73935,12 +73980,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Programação diária (MSUTWI), obtido em 29/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CMO semanal (subsistema SE, agregado), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.976 de 5.976 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -73962,12 +74007,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Programação diária (MSUTWI), obtido em 29/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CMO semanal (subsistema SE, agregado), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>TEIFa e TEIP recalculadas conferidas com as publicadas em Taxas TEIFa e TEIP: 0 de 4 meses reproduzidos (diferença máxima de 2,067 p.p.); DISPF conferido com as horas por estado operativo (Parâmetros das taxas TEIFa e TEIP): 52 divergências (meses-unidade), listadas na aba ONS_DIVERGENCIAS; potência autorizada e estado conferidos com os parâmetros do projeto: sem divergência; programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.976 de 5.976 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -73989,7 +74034,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; parâmetros do projeto (origem na tabela de parâmetros)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -74016,7 +74061,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -74043,7 +74088,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -74070,7 +74115,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -74097,7 +74142,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -74124,7 +74169,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -74151,7 +74196,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -74232,7 +74277,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>parâmetros do projeto (origem na tabela de parâmetros); Geração por usina (id ONS MSUTWI), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Programação diária (MSUTWI), obtido em 29/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CMO semanal (subsistema SE, agregado), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -74259,7 +74304,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -74286,7 +74331,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -74313,7 +74358,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -74340,7 +74385,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Programação diária (MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Programação diária (MSUTWI), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -74367,7 +74412,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Programação diária (MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Programação diária (MSUTWI), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -74394,12 +74439,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -74421,12 +74466,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -74448,7 +74493,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -74475,12 +74520,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.976 de 5.976 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -74502,12 +74547,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes; geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.976 de 5.976 horas coincidentes (100,0%); geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -74529,12 +74574,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -74556,12 +74601,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -74583,7 +74628,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CMO semanal (subsistema SE, agregado), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -74610,7 +74655,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CMO semanal (subsistema SE, agregado), obtido em 29/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -74637,12 +74682,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Programação diária (MSUTWI), obtido em 26/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026</t>
+          <t>Programação diária (MSUTWI), obtido em 29/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.784 de 5.784 horas coincidentes (100,0%), 96 horas só numa das fontes</t>
+          <t>programação diária conferida com o programado da Geração térmica por motivo de despacho (G3): 5.976 de 5.976 horas coincidentes (100,0%)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -74664,12 +74709,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -74691,12 +74736,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026</t>
+          <t>Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.137 de 46.267 horas coincidentes (99,7%), 130 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
+          <t>geração verificada da Geração térmica por motivo de despacho conferida com Geração por usina (G4): 46.337 de 46.459 horas coincidentes (99,7%), 122 divergências, listadas na aba CONF_G4_DIVERGENCIAS, 5 horas só numa das fontes</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -74718,7 +74763,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -74745,7 +74790,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -74772,7 +74817,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -74799,7 +74844,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -74826,7 +74871,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -74853,7 +74898,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -74880,7 +74925,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -74907,7 +74952,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -74934,7 +74979,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -74961,7 +75006,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026</t>
+          <t>Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -74988,7 +75033,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Programação diária (MSUTWI), obtido em 26/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 26/10/2026; Geração por usina (id ONS MSUTWI), obtido em 26/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 26/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS ), data de obtenção não registrada; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 22/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 21/10/2026; CMO semanal (subsistema SE, agregado), obtido em 20/10/2026</t>
+          <t>Indicadores de disponibilidade por unidade geradora, base mensal (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Indicadores de disponibilidade por unidade geradora, base anual (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Parâmetros das taxas TEIFa e TEIP (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Taxas TEIFa Oper e TEIP Oper (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Programação diária (MSUTWI), obtido em 29/10/2026; Disponibilidade por usina (id ONS MSUTWI), obtido em 29/10/2026; Geração por usina (id ONS MSUTWI), obtido em 29/10/2026; Modalidade das usinas (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Composição dos conjuntos de usinas (conjunto de usinas, id ONS ), data de obtenção não registrada; Capacidade de geração (CEG UTE.GN.MS.027075-0.01), obtido em 29/10/2026; Geração térmica por motivo de despacho (CEG UTE.GN.MS.027075-0.01; códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CVU das usinas térmicas (códigos de planejamento 34, 334, 434), obtido em 29/10/2026; CMO semanal (subsistema SE, agregado), obtido em 29/10/2026</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -75203,7 +75248,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19.03076012569833</v>
+        <v>19.09742090201465</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -75293,10 +75338,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.608160113812726</v>
+        <v>6.597543388429752</v>
       </c>
       <c r="D2" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="3">
@@ -75309,10 +75354,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>6.551910501810657</v>
+        <v>6.541378615702479</v>
       </c>
       <c r="D3" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="4">
@@ -75325,10 +75370,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>6.524426539058458</v>
+        <v>6.513950929752066</v>
       </c>
       <c r="D4" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="5">
@@ -75341,10 +75386,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>6.56585248447205</v>
+        <v>6.555292506459948</v>
       </c>
       <c r="D5" t="n">
-        <v>1932</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="6">
@@ -75357,10 +75402,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.605391619244697</v>
+        <v>6.594772727272727</v>
       </c>
       <c r="D6" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="7">
@@ -75373,10 +75418,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>6.675572463768116</v>
+        <v>6.664848062015504</v>
       </c>
       <c r="D7" t="n">
-        <v>1932</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="8">
@@ -75389,10 +75434,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.65474236937403</v>
+        <v>6.644054752066116</v>
       </c>
       <c r="D8" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="9">
@@ -75405,10 +75450,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6.705889032591826</v>
+        <v>6.695121900826446</v>
       </c>
       <c r="D9" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="10">
@@ -75421,10 +75466,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>6.548368339368857</v>
+        <v>6.537847107438017</v>
       </c>
       <c r="D10" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="11">
@@ -75437,10 +75482,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.372177444386963</v>
+        <v>6.361925619834711</v>
       </c>
       <c r="D11" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="12">
@@ -75453,10 +75498,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.137781427832385</v>
+        <v>6.12791270661157</v>
       </c>
       <c r="D12" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="13">
@@ -75469,10 +75514,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6.086363683393689</v>
+        <v>6.076339876033058</v>
       </c>
       <c r="D13" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="14">
@@ -75485,10 +75530,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>6.07680703569581</v>
+        <v>6.066705578512397</v>
       </c>
       <c r="D14" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="15">
@@ -75501,10 +75546,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.97120563890326</v>
+        <v>5.961281508264462</v>
       </c>
       <c r="D15" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="16">
@@ -75517,10 +75562,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.964300207039337</v>
+        <v>5.954478552971576</v>
       </c>
       <c r="D16" t="n">
-        <v>1932</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="17">
@@ -75533,10 +75578,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.959044254658385</v>
+        <v>5.949188630490956</v>
       </c>
       <c r="D17" t="n">
-        <v>1932</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="18">
@@ -75549,10 +75594,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.075216502845318</v>
+        <v>6.08049819214876</v>
       </c>
       <c r="D18" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="19">
@@ -75565,10 +75610,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>6.639949301603726</v>
+        <v>6.72444292355372</v>
       </c>
       <c r="D19" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="20">
@@ -75581,10 +75626,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>7.14187247801345</v>
+        <v>7.276291064049587</v>
       </c>
       <c r="D20" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="21">
@@ -75597,10 +75642,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>7.458722567287785</v>
+        <v>7.594545219638243</v>
       </c>
       <c r="D21" t="n">
-        <v>1932</v>
+        <v>1935</v>
       </c>
     </row>
     <row r="22">
@@ -75613,10 +75658,10 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>7.599786601138128</v>
+        <v>7.734668646694215</v>
       </c>
       <c r="D22" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="23">
@@ -75629,10 +75674,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.581912829798241</v>
+        <v>7.718685433884297</v>
       </c>
       <c r="D23" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="24">
@@ -75645,10 +75690,10 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7.500553802379721</v>
+        <v>7.638267045454545</v>
       </c>
       <c r="D24" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="25">
@@ -75661,10 +75706,10 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>7.081958872219348</v>
+        <v>7.089608987603306</v>
       </c>
       <c r="D25" t="n">
-        <v>1933</v>
+        <v>1936</v>
       </c>
     </row>
   </sheetData>
@@ -75715,7 +75760,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1320</v>
+        <v>1331</v>
       </c>
     </row>
   </sheetData>
@@ -75995,7 +76040,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-10-24 23:00:00</t>
+          <t>2026-10-27 23:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
